--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.3208</v>
+        <v>16.82469</v>
       </c>
       <c r="D2" t="n">
-        <v>16.98164</v>
+        <v>16.56289</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82708</v>
+        <v>16.7579</v>
       </c>
       <c r="F2" t="n">
-        <v>42.44855</v>
+        <v>42.21724</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0508</v>
+        <v>0.04995</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81059</v>
+        <v>1.82147</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.83376</v>
+        <v>16.67813</v>
       </c>
       <c r="D3" t="n">
-        <v>16.25366</v>
+        <v>16.55163</v>
       </c>
       <c r="E3" t="n">
-        <v>16.49399</v>
+        <v>16.5692</v>
       </c>
       <c r="F3" t="n">
-        <v>43.45818</v>
+        <v>42.51959</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04979</v>
+        <v>0.05026</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79898</v>
+        <v>1.81747</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.05042</v>
+        <v>17.08447</v>
       </c>
       <c r="D4" t="n">
-        <v>16.28049</v>
+        <v>16.5018</v>
       </c>
       <c r="E4" t="n">
-        <v>16.69313</v>
+        <v>16.95892</v>
       </c>
       <c r="F4" t="n">
-        <v>42.40173</v>
+        <v>42.47348</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05068</v>
+        <v>0.05177</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83713</v>
+        <v>1.80428</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.56862</v>
+        <v>16.72446</v>
       </c>
       <c r="D6" t="n">
-        <v>15.95225</v>
+        <v>16.11927</v>
       </c>
       <c r="E6" t="n">
-        <v>16.4536</v>
+        <v>16.12561</v>
       </c>
       <c r="F6" t="n">
-        <v>21.50011</v>
+        <v>21.91578</v>
       </c>
       <c r="G6" t="n">
-        <v>34.34816</v>
+        <v>34.34098</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.71385</v>
+        <v>16.61746</v>
       </c>
       <c r="D7" t="n">
-        <v>15.75983</v>
+        <v>15.82233</v>
       </c>
       <c r="E7" t="n">
-        <v>16.17955</v>
+        <v>16.49914</v>
       </c>
       <c r="F7" t="n">
-        <v>22.27511</v>
+        <v>21.79708</v>
       </c>
       <c r="G7" t="n">
-        <v>33.25223</v>
+        <v>34.15423</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.50699</v>
+        <v>16.67579</v>
       </c>
       <c r="D8" t="n">
-        <v>15.61168</v>
+        <v>16.06013</v>
       </c>
       <c r="E8" t="n">
-        <v>15.94666</v>
+        <v>16.61738</v>
       </c>
       <c r="F8" t="n">
-        <v>21.75514</v>
+        <v>22.03855</v>
       </c>
       <c r="G8" t="n">
-        <v>34.68907</v>
+        <v>34.82998</v>
       </c>
     </row>
   </sheetData>
